--- a/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
   <si>
     <t>ZIMV</t>
   </si>
@@ -656,73 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -735,47 +735,50 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>457400</v>
+      </c>
+      <c r="E8" s="3">
         <v>202900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>224900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>225400</v>
       </c>
-      <c r="G8" s="3">
-        <v>229100</v>
-      </c>
       <c r="H8" s="3">
+        <v>463300</v>
+      </c>
+      <c r="I8" s="3">
         <v>214600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>234600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>235600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>261600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>753000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>274900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>637500</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -788,47 +791,50 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>167100</v>
+      </c>
+      <c r="E9" s="3">
         <v>65200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>74500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>71000</v>
       </c>
-      <c r="G9" s="3">
-        <v>74300</v>
-      </c>
       <c r="H9" s="3">
+        <v>242700</v>
+      </c>
+      <c r="I9" s="3">
         <v>59600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>81100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>85800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>125900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>259900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>92100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>220800</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -841,47 +847,50 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>290400</v>
+      </c>
+      <c r="E10" s="3">
         <v>137700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>150400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>154400</v>
       </c>
-      <c r="G10" s="3">
-        <v>154800</v>
-      </c>
       <c r="H10" s="3">
+        <v>220600</v>
+      </c>
+      <c r="I10" s="3">
         <v>155000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>153500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>149800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>135700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>493100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>182800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>416700</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -894,8 +903,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -915,47 +927,48 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E12" s="3">
         <v>11500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>46400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>14500</v>
+      </c>
+      <c r="J12" s="3">
         <v>15300</v>
       </c>
-      <c r="H12" s="3">
-        <v>14500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>15300</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>43900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>36100</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -968,8 +981,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1021,47 +1037,50 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E14" s="3">
         <v>4400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>9800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6700</v>
       </c>
-      <c r="G14" s="3">
-        <v>8900</v>
-      </c>
       <c r="H14" s="3">
+        <v>29100</v>
+      </c>
+      <c r="I14" s="3">
         <v>8400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>153200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1074,47 +1093,50 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E15" s="3">
         <v>20600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20500</v>
       </c>
-      <c r="G15" s="3">
-        <v>20700</v>
-      </c>
       <c r="H15" s="3">
+        <v>27000</v>
+      </c>
+      <c r="I15" s="3">
         <v>19400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>20900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>65000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>22100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>63400</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1127,8 +1149,11 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1145,47 +1170,48 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>488400</v>
+      </c>
+      <c r="E17" s="3">
         <v>219100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>246700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>241600</v>
       </c>
-      <c r="G17" s="3">
-        <v>253500</v>
-      </c>
       <c r="H17" s="3">
+        <v>509800</v>
+      </c>
+      <c r="I17" s="3">
         <v>231300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>256100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>268200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>326900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>788200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>270300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>864700</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1198,47 +1224,50 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-16200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-21800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-24400</v>
-      </c>
       <c r="H18" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-16700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-21500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-32600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-65300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-35200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-227200</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1251,8 +1280,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1272,47 +1304,48 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
-        <v>2600</v>
-      </c>
       <c r="H20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1325,47 +1358,50 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>91100</v>
+      </c>
+      <c r="E21" s="3">
         <v>14300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15600</v>
       </c>
-      <c r="G21" s="3">
-        <v>8500</v>
-      </c>
       <c r="H21" s="3">
+        <v>79200</v>
+      </c>
+      <c r="I21" s="3">
         <v>14100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-31400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>60100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>39400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-126100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,47 +1414,50 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E22" s="3">
         <v>9200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>9000</v>
       </c>
       <c r="F22" s="3">
         <v>9000</v>
       </c>
       <c r="G22" s="3">
-        <v>6400</v>
+        <v>9000</v>
       </c>
       <c r="H22" s="3">
+        <v>10900</v>
+      </c>
+      <c r="I22" s="3">
         <v>6200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1431,47 +1470,50 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-26000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-28200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-22300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-26300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-33100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-65400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-35900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-226500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1484,47 +1526,50 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-20400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-6900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4000</v>
       </c>
-      <c r="G24" s="3">
-        <v>2100</v>
-      </c>
       <c r="H24" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="I24" s="3">
         <v>-23100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-17600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-31300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-11000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1537,8 +1582,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1590,47 +1638,50 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-30000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-30300</v>
-      </c>
       <c r="H26" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-60700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-215500</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1643,47 +1694,50 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-30000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-30300</v>
-      </c>
       <c r="H27" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="I27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-60700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-215600</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1696,8 +1750,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1749,31 +1806,34 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
+        <v>-337200</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>-17000</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1802,8 +1862,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1855,8 +1918,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1908,47 +1974,50 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
-        <v>-2600</v>
-      </c>
       <c r="H32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1961,47 +2030,50 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-393300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-30000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-30300</v>
-      </c>
       <c r="H33" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-60700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>36500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-215600</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2014,8 +2086,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2067,47 +2142,50 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-393300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-30000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-30300</v>
-      </c>
       <c r="H35" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-60700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>36500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-215600</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2120,52 +2198,55 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2178,8 +2259,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2199,8 +2283,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2220,41 +2305,42 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E41" s="3">
         <v>75400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>66200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>66400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>89600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>116000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>130100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>104300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2273,8 +2359,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2326,41 +2415,44 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E43" s="3">
         <v>153900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>168100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>175000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>177400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>172700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>188400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>180100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>164200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>170200</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2379,41 +2471,44 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>79600</v>
+      </c>
+      <c r="E44" s="3">
         <v>213700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>227500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>231100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>233900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>224200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>226500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>239300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>246800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>274700</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2432,41 +2527,44 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>266600</v>
+      </c>
+      <c r="E45" s="3">
         <v>54500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>45500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>31700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>25400</v>
       </c>
       <c r="K45" s="3">
         <v>25400</v>
       </c>
       <c r="L45" s="3">
+        <v>25400</v>
+      </c>
+      <c r="M45" s="3">
         <v>22700</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2485,41 +2583,44 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>482900</v>
+      </c>
+      <c r="E46" s="3">
         <v>497600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>507400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>504200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>537900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>546200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>573900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>549100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>536800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>491700</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2538,8 +2639,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2591,41 +2695,44 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E48" s="3">
         <v>121400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>129700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>139300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>148400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>150300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>162900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>170500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>180200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>180700</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2644,41 +2751,44 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>376500</v>
+      </c>
+      <c r="E49" s="3">
         <v>850600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>885800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>905200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>915000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>893900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>944600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>999000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1034000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1066700</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,8 +2807,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2750,8 +2863,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2803,41 +2919,44 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>291800</v>
+      </c>
+      <c r="E52" s="3">
         <v>38300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>37700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>40800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>38900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>51200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>55600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>75700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>69800</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,8 +2975,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2909,41 +3031,44 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1205300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1507900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1560500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1588100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1642100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1629400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1732600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1774300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1826700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1808900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2962,8 +3087,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2983,8 +3111,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3004,41 +3133,42 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E57" s="3">
         <v>51300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>59400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>52600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>39100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>45000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>40500</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3057,13 +3187,16 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>0</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>3</v>
@@ -3074,8 +3207,8 @@
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H58" s="3">
-        <v>14000</v>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I58" s="3">
         <v>14000</v>
@@ -3084,14 +3217,14 @@
         <v>14000</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>33000</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3110,41 +3243,44 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>145800</v>
+      </c>
+      <c r="E59" s="3">
         <v>119900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>130300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>143900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>173300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>162400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>189700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>166400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>139600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>128200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3163,41 +3299,44 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>173600</v>
+      </c>
+      <c r="E60" s="3">
         <v>171200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>189700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>196500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>217300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>217500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>246800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>219500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>184600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>201700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,41 +3355,44 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>508800</v>
+      </c>
+      <c r="E61" s="3">
         <v>515500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>522300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>522000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>532200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>535500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>538700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>541900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>4900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3269,41 +3411,44 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>113400</v>
+      </c>
+      <c r="E62" s="3">
         <v>111000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>120700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>125900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>133900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>142600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>182600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>200400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>190700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>200000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3322,8 +3467,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3375,8 +3523,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3428,8 +3579,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3481,41 +3635,44 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>795900</v>
+      </c>
+      <c r="E66" s="3">
         <v>797700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>832700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>844500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>883500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>895600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>968000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>961800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>375300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>406600</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,8 +3691,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3555,8 +3715,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3608,8 +3769,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3661,8 +3825,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3714,8 +3881,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3767,35 +3937,38 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-440800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-106000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-100900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-77500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-47500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-17200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-18000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3808,8 +3981,8 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q72" s="3">
         <v>0</v>
@@ -3820,8 +3993,11 @@
       <c r="S72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3873,8 +4049,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3926,8 +4105,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3979,41 +4161,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>409500</v>
+      </c>
+      <c r="E76" s="3">
         <v>710200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>727800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>743600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>758600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>733800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>764600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>812500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1451400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1402300</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4032,8 +4217,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4085,52 +4273,55 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4143,47 +4334,50 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-393300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-30000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-30300</v>
-      </c>
       <c r="H81" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-60700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>36500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-215600</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4196,8 +4390,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4217,47 +4414,48 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>121700</v>
+      </c>
+      <c r="E83" s="3">
         <v>30500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>32000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>32600</v>
       </c>
-      <c r="G83" s="3">
-        <v>30300</v>
-      </c>
       <c r="H83" s="3">
+        <v>122800</v>
+      </c>
+      <c r="I83" s="3">
         <v>30200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>32600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>95700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>34100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4270,8 +4468,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4323,8 +4524,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4376,8 +4580,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4429,8 +4636,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4482,8 +4692,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4535,47 +4748,50 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E89" s="3">
         <v>22600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7200</v>
       </c>
-      <c r="G89" s="3">
-        <v>-8900</v>
-      </c>
       <c r="H89" s="3">
+        <v>24600</v>
+      </c>
+      <c r="I89" s="3">
         <v>2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>40600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>21400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>42900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>91700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4588,8 +4804,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4609,47 +4828,48 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-34200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3700</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4882,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4715,8 +4938,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4768,47 +4994,50 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5800</v>
       </c>
-      <c r="G94" s="3">
-        <v>-5600</v>
-      </c>
       <c r="H94" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="I94" s="3">
         <v>-8900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-37900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-20100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-29400</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4821,8 +5050,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4842,8 +5074,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4860,17 +5093,17 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-540600</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-540600</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4895,8 +5128,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4948,8 +5184,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5001,8 +5240,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5054,47 +5296,50 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10900</v>
       </c>
-      <c r="G100" s="3">
-        <v>-16500</v>
-      </c>
       <c r="H100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I100" s="3">
         <v>-3500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>22200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>79800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-74300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>27800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5107,47 +5352,50 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
-        <v>4600</v>
-      </c>
       <c r="H101" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="I101" s="3">
         <v>-4500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5160,47 +5408,50 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>9200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-23200</v>
       </c>
-      <c r="G102" s="3">
-        <v>-26400</v>
-      </c>
       <c r="H102" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="I102" s="3">
         <v>-14000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>76300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5211,6 +5462,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>ZIMV</t>
   </si>
@@ -656,76 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -738,50 +739,53 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E8" s="3">
         <v>457400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>202900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>224900</v>
       </c>
-      <c r="G8" s="3">
-        <v>225400</v>
-      </c>
       <c r="H8" s="3">
+        <v>120400</v>
+      </c>
+      <c r="I8" s="3">
         <v>463300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>214600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>234600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>235600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>261600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>753000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>274900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>637500</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -794,50 +798,53 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E9" s="3">
         <v>167100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>65200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>74500</v>
       </c>
-      <c r="G9" s="3">
-        <v>71000</v>
-      </c>
       <c r="H9" s="3">
+        <v>43100</v>
+      </c>
+      <c r="I9" s="3">
         <v>242700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>59600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>81100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>85800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>125900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>259900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>92100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>220800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -850,50 +857,53 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E10" s="3">
         <v>290400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>137700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>150400</v>
       </c>
-      <c r="G10" s="3">
-        <v>154400</v>
-      </c>
       <c r="H10" s="3">
+        <v>77300</v>
+      </c>
+      <c r="I10" s="3">
         <v>220600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>155000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>153500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>149800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>135700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>493100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>182800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>416700</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -906,8 +916,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -928,50 +941,51 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E12" s="3">
         <v>26200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13200</v>
       </c>
-      <c r="G12" s="3">
-        <v>15400</v>
-      </c>
       <c r="H12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I12" s="3">
         <v>46400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>43900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>36100</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -984,8 +998,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1040,50 +1057,53 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E14" s="3">
         <v>19700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>9800</v>
       </c>
-      <c r="G14" s="3">
-        <v>6700</v>
-      </c>
       <c r="H14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I14" s="3">
         <v>29100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>153200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1096,50 +1116,53 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E15" s="3">
         <v>26500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20700</v>
       </c>
-      <c r="G15" s="3">
-        <v>20500</v>
-      </c>
       <c r="H15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I15" s="3">
         <v>27000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>65000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>22100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>63400</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1152,8 +1175,11 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1171,50 +1197,51 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>120900</v>
+      </c>
+      <c r="E17" s="3">
         <v>488400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>219100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>246700</v>
       </c>
-      <c r="G17" s="3">
-        <v>241600</v>
-      </c>
       <c r="H17" s="3">
+        <v>126600</v>
+      </c>
+      <c r="I17" s="3">
         <v>509800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>231300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>256100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>268200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>326900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>788200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>270300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>864700</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1227,50 +1254,53 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-31000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-16200</v>
-      </c>
       <c r="H18" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-46500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-21500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-32600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-65300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-35200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-227200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1283,8 +1313,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1305,50 +1338,51 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-900</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1361,50 +1395,53 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E21" s="3">
         <v>91100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>14300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10700</v>
       </c>
-      <c r="G21" s="3">
-        <v>15600</v>
-      </c>
       <c r="H21" s="3">
+        <v>26400</v>
+      </c>
+      <c r="I21" s="3">
         <v>79200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-31400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>60100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>39400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-126100</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1417,50 +1454,53 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E22" s="3">
         <v>20200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>9000</v>
       </c>
       <c r="G22" s="3">
         <v>9000</v>
       </c>
       <c r="H22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I22" s="3">
         <v>10900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1473,50 +1513,53 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-50800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-30200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-26000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-54500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-22300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-33100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-65400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-35900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-226500</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1529,50 +1572,53 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>5200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-20400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-6900</v>
       </c>
-      <c r="G24" s="3">
-        <v>4000</v>
-      </c>
       <c r="H24" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I24" s="3">
         <v>-7600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-23100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-17600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-31300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11000</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1585,8 +1631,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1641,50 +1690,53 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-56000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23400</v>
       </c>
-      <c r="G26" s="3">
-        <v>-30000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="I26" s="3">
         <v>-46900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-60700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>36500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-215500</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1697,50 +1749,53 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-56000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23400</v>
       </c>
-      <c r="G27" s="3">
-        <v>-30000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="I27" s="3">
         <v>-46900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-60700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>36500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-215600</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1753,8 +1808,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1809,17 +1867,20 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E29" s="3">
         <v>-337200</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1827,16 +1888,16 @@
         <v>3</v>
       </c>
       <c r="H29" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="I29" s="3">
         <v>-17000</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1865,8 +1926,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1921,8 +1985,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1977,50 +2044,53 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
-        <v>900</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,50 +2103,53 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-393300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-30000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-63900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-60700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>36500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-215600</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2089,8 +2162,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2145,50 +2221,53 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-393300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-30000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-63900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-60700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>36500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-215600</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2201,55 +2280,58 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2262,8 +2344,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2284,8 +2369,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2306,44 +2392,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E41" s="3">
         <v>71500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>75400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>66200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>66400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>89600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>116000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>130100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>104300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,8 +2449,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2418,44 +2508,47 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E43" s="3">
         <v>65200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>153900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>168100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>175000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>177400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>172700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>188400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>180100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>164200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>170200</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2474,44 +2567,47 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E44" s="3">
         <v>79600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>213700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>227500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>231100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>233900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>224200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>226500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>239300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>246800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>274700</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,44 +2626,47 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>265400</v>
+      </c>
+      <c r="E45" s="3">
         <v>266600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>54500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>45500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>37000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>25400</v>
       </c>
       <c r="L45" s="3">
         <v>25400</v>
       </c>
       <c r="M45" s="3">
+        <v>25400</v>
+      </c>
+      <c r="N45" s="3">
         <v>22700</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2586,44 +2685,47 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>455100</v>
+      </c>
+      <c r="E46" s="3">
         <v>482900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>497600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>507400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>504200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>537900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>546200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>573900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>549100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>536800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>491700</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2642,8 +2744,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2698,44 +2803,47 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E48" s="3">
         <v>54200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>121400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>129700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>139300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>148400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>150300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>162900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>170500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>180200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>180700</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2754,44 +2862,47 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>369800</v>
+      </c>
+      <c r="E49" s="3">
         <v>376500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>850600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>885800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>905200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>915000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>893900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>944600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>999000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1034000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1066700</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2810,8 +2921,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2866,8 +2980,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2922,44 +3039,47 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>294500</v>
+      </c>
+      <c r="E52" s="3">
         <v>291800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>38300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>37700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>39400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>38900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>51200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>55600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>75700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>69800</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,8 +3098,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3034,44 +3157,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1171600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1205300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1507900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1560500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1588100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1642100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1629400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1732600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1774300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1826700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1808900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3090,8 +3216,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3112,8 +3241,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3134,44 +3264,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E57" s="3">
         <v>27800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>51300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>59400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>52600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>39100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>40500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3190,16 +3321,19 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+        <v>7000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -3210,8 +3344,8 @@
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I58" s="3">
-        <v>14000</v>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J58" s="3">
         <v>14000</v>
@@ -3220,14 +3354,14 @@
         <v>14000</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>33000</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3246,44 +3380,47 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>135700</v>
+      </c>
+      <c r="E59" s="3">
         <v>145800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>119900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>130300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>143900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>173300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>162400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>189700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>166400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>139600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>128200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,44 +3439,47 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>169600</v>
+      </c>
+      <c r="E60" s="3">
         <v>173600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>171200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>189700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>196500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>217300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>217500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>246800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>219500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>184600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>201700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3358,44 +3498,47 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>502100</v>
+      </c>
+      <c r="E61" s="3">
         <v>508800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>515500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>522300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>522000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>532200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>535500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>538700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>541900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>4900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3414,44 +3557,47 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>111600</v>
+      </c>
+      <c r="E62" s="3">
         <v>113400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>111000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>120700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>125900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>133900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>142600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>182600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>200400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>190700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>200000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3616,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3526,8 +3675,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3582,8 +3734,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3638,44 +3793,47 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>783300</v>
+      </c>
+      <c r="E66" s="3">
         <v>795900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>797700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>832700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>844500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>883500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>895600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>968000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>961800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>375300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>406600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,8 +3852,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3716,8 +3877,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3772,8 +3934,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3828,8 +3993,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3884,8 +4052,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3940,38 +4111,41 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-448600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-440800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-106000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-100900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-77500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-47500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-17200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-18000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-9300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3984,8 +4158,8 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
@@ -3996,8 +4170,11 @@
       <c r="T72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4052,8 +4229,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4108,8 +4288,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4164,44 +4347,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>388300</v>
+      </c>
+      <c r="E76" s="3">
         <v>409500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>710200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>727800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>743600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>758600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>733800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>764600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>812500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1451400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1402300</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4220,8 +4406,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4276,55 +4465,58 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4337,50 +4529,53 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-393300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-30000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-63900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-60700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>36500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-215600</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4393,8 +4588,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4415,50 +4613,51 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E83" s="3">
         <v>121700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>32000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>32600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>122800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>30200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>29700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>32600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>95700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>34100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100200</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4471,8 +4670,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4527,8 +4729,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4583,8 +4788,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4639,8 +4847,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4695,8 +4906,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4751,50 +4965,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E89" s="3">
         <v>37100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>22600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>40600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>42900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>91700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4807,8 +5024,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4829,50 +5049,51 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-34200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3700</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4885,8 +5106,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4941,8 +5165,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4997,50 +5224,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-28700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-37900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-20100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-29400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5053,8 +5283,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5075,8 +5308,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5093,20 +5327,20 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-540600</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-540600</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -5131,8 +5365,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5187,8 +5424,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5243,8 +5483,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5299,50 +5542,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-25700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>22200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>79800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-74300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>27800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5355,50 +5601,53 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>1900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5411,50 +5660,53 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>76300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5465,6 +5717,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
   <si>
     <t>ZIMV</t>
   </si>
@@ -656,80 +656,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -742,53 +743,56 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>116800</v>
+      </c>
+      <c r="E8" s="3">
         <v>118200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>457400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>202900</v>
       </c>
-      <c r="G8" s="3">
-        <v>224900</v>
-      </c>
       <c r="H8" s="3">
+        <v>118600</v>
+      </c>
+      <c r="I8" s="3">
         <v>120400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>463300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>214600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>234600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>235600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>261600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>753000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>274900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>637500</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,53 +805,56 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E9" s="3">
         <v>44300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>167100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>65200</v>
       </c>
-      <c r="G9" s="3">
-        <v>74500</v>
-      </c>
       <c r="H9" s="3">
+        <v>44500</v>
+      </c>
+      <c r="I9" s="3">
         <v>43100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>242700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>59600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>81100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>85800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>125900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>259900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>92100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>220800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -860,53 +867,56 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E10" s="3">
         <v>73900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>290400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>137700</v>
       </c>
-      <c r="G10" s="3">
-        <v>150400</v>
-      </c>
       <c r="H10" s="3">
+        <v>74100</v>
+      </c>
+      <c r="I10" s="3">
         <v>77300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>220600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>155000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>153500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>149800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>135700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>493100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>182800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>416700</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,8 +929,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -942,53 +955,54 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>6700</v>
+        <v>6600</v>
       </c>
       <c r="E12" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F12" s="3">
         <v>26200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11500</v>
       </c>
-      <c r="G12" s="3">
-        <v>13200</v>
-      </c>
       <c r="H12" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I12" s="3">
         <v>7200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>46400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>43900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>36100</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1001,8 +1015,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1060,53 +1077,56 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="3">
         <v>3600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>19700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4400</v>
       </c>
-      <c r="G14" s="3">
-        <v>9800</v>
-      </c>
       <c r="H14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I14" s="3">
         <v>2500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>29100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>153200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1119,8 +1139,11 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1128,44 +1151,44 @@
         <v>6000</v>
       </c>
       <c r="E15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F15" s="3">
         <v>26500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>20700</v>
       </c>
       <c r="H15" s="3">
         <v>6800</v>
       </c>
       <c r="I15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J15" s="3">
         <v>27000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>19900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>20900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>65000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>22100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>63400</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1178,8 +1201,11 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1198,53 +1224,54 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>120900</v>
+        <v>123500</v>
       </c>
       <c r="E17" s="3">
+        <v>121000</v>
+      </c>
+      <c r="F17" s="3">
         <v>488400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>219100</v>
       </c>
-      <c r="G17" s="3">
-        <v>246700</v>
-      </c>
       <c r="H17" s="3">
+        <v>123000</v>
+      </c>
+      <c r="I17" s="3">
         <v>126600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>509800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>231300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>256100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>268200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>326900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>788200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>270300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>864700</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1257,53 +1284,56 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2700</v>
+        <v>-6700</v>
       </c>
       <c r="E18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-31000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-21800</v>
-      </c>
       <c r="H18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-6200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-46500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-21500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-32600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-65300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-35200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-227200</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1316,8 +1346,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1339,53 +1372,54 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-300</v>
+        <v>5000</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>600</v>
+      </c>
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1398,53 +1432,56 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5400</v>
+        <v>6800</v>
       </c>
       <c r="E21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F21" s="3">
         <v>91100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>14300</v>
       </c>
-      <c r="G21" s="3">
-        <v>10700</v>
-      </c>
       <c r="H21" s="3">
-        <v>26400</v>
+        <v>28100</v>
       </c>
       <c r="I21" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J21" s="3">
         <v>79200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-31400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>60100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>39400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-126100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1457,53 +1494,56 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>4400</v>
+        <v>5100</v>
       </c>
       <c r="E22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F22" s="3">
         <v>20200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9200</v>
       </c>
-      <c r="G22" s="3">
-        <v>9000</v>
-      </c>
       <c r="H22" s="3">
-        <v>5100</v>
+        <v>5900</v>
       </c>
       <c r="I22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J22" s="3">
         <v>10900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1516,53 +1556,56 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-7400</v>
+        <v>-6800</v>
       </c>
       <c r="E23" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-50800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25500</v>
       </c>
-      <c r="G23" s="3">
-        <v>-30200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="I23" s="3">
         <v>-11300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-54500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-22300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-33100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-65400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-35900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-226500</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1575,53 +1618,56 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E24" s="3">
         <v>4100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-20400</v>
       </c>
-      <c r="G24" s="3">
-        <v>-6900</v>
-      </c>
       <c r="H24" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I24" s="3">
         <v>5100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-23100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-17600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-31300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1634,8 +1680,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1693,53 +1742,56 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-11500</v>
+        <v>-9600</v>
       </c>
       <c r="E26" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-56000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5100</v>
       </c>
-      <c r="G26" s="3">
-        <v>-23400</v>
-      </c>
       <c r="H26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-16400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-46900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-60700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-34600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>36500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-215500</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1752,53 +1804,56 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-11500</v>
+        <v>-9600</v>
       </c>
       <c r="E27" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-56000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5100</v>
       </c>
-      <c r="G27" s="3">
-        <v>-23400</v>
-      </c>
       <c r="H27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="I27" s="3">
         <v>-16400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-46900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-60700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-34600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>36500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-215600</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1811,8 +1866,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1870,37 +1928,40 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>3700</v>
+        <v>5500</v>
       </c>
       <c r="E29" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F29" s="3">
         <v>-337200</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H29" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="I29" s="3">
         <v>-13600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-17000</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -1929,8 +1990,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1988,8 +2052,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2047,53 +2114,56 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>300</v>
+        <v>-5000</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2106,53 +2176,56 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-393300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-63900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-60700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-34600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>36500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-215600</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2165,8 +2238,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2224,53 +2300,56 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-393300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-63900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-60700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-34600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>36500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-215600</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,58 +2362,61 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2347,8 +2429,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2370,8 +2455,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2393,47 +2479,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E41" s="3">
         <v>43500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>71500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>75400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>66200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>66400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>89600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>116000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>130100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>104300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24100</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2452,8 +2539,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2511,47 +2601,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E43" s="3">
         <v>68900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>65200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>153900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>168100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>175000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>177400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>172700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>188400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>180100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>164200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>170200</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2570,47 +2663,50 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E44" s="3">
         <v>77200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>79600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>213700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>227500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>231100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>233900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>224200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>226500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>239300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>246800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>274700</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2629,47 +2725,50 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E45" s="3">
         <v>265400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>266600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>54500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>45500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>37000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>25400</v>
       </c>
       <c r="M45" s="3">
         <v>25400</v>
       </c>
       <c r="N45" s="3">
+        <v>25400</v>
+      </c>
+      <c r="O45" s="3">
         <v>22700</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2688,47 +2787,50 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>273900</v>
+      </c>
+      <c r="E46" s="3">
         <v>455100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>482900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>497600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>507400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>504200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>537900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>546200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>573900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>549100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>536800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>491700</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2747,31 +2849,34 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>60300</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2806,47 +2911,50 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E48" s="3">
         <v>52100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>121400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>129700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>139300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>148400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>150300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>162900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>170500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>180200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>180700</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2865,47 +2973,50 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>362800</v>
+      </c>
+      <c r="E49" s="3">
         <v>369800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>376500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>850600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>885800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>905200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>915000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>893900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>944600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>999000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1034000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1066700</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2924,8 +3035,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2983,8 +3097,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3042,47 +3159,50 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E52" s="3">
         <v>294500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>291800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>38300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>37700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>39400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>40800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>51200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>55600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>75700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>69800</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3101,8 +3221,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3160,47 +3283,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>789800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1171600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1205300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1507900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1560500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1588100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1642100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1629400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1732600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1774300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1826700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1808900</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,8 +3345,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3242,8 +3371,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3265,47 +3395,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E57" s="3">
         <v>27000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>51300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>59400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>52600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>44000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>40500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3324,19 +3455,22 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3">
         <v>7000</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+      <c r="F58" s="3">
+        <v>0</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -3347,8 +3481,8 @@
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J58" s="3">
-        <v>14000</v>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>14000</v>
@@ -3357,14 +3491,14 @@
         <v>14000</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>33000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3383,47 +3517,50 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E59" s="3">
         <v>135700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>145800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>119900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>130300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>143900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>173300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>162400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>189700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>166400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>139600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>128200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3442,47 +3579,50 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>141100</v>
+      </c>
+      <c r="E60" s="3">
         <v>169600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>173600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>171200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>189700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>196500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>217300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>217500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>246800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>219500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>184600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>201700</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3501,47 +3641,50 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>235100</v>
+      </c>
+      <c r="E61" s="3">
         <v>502100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>508800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>515500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>522300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>522000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>532200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>535500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>538700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>541900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>4900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3560,47 +3703,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E62" s="3">
         <v>111600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>113400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>111000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>120700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>125900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>133900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>142600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>182600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>200400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>190700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>200000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3619,8 +3765,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3678,8 +3827,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3737,8 +3889,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3796,47 +3951,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>395700</v>
+      </c>
+      <c r="E66" s="3">
         <v>783300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>795900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>797700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>832700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>844500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>883500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>895600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>968000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>961800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>375300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>406600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3855,8 +4013,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3878,8 +4039,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3937,8 +4099,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3996,8 +4161,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4055,8 +4223,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4114,41 +4285,44 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-452600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-448600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-440800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-106000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-100900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-77500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-47500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-17200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-18000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-9300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4161,8 +4335,8 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S72" s="3">
         <v>0</v>
@@ -4173,8 +4347,11 @@
       <c r="U72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4232,8 +4409,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4291,8 +4471,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4350,47 +4533,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>394100</v>
+      </c>
+      <c r="E76" s="3">
         <v>388300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>409500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>710200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>727800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>743600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>758600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>733800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>764600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>812500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1451400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1402300</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4409,8 +4595,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4468,58 +4657,61 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4532,53 +4724,56 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-393300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-63900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-60700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-34600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>36500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-215600</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4591,8 +4786,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4614,53 +4812,54 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E83" s="3">
         <v>8400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>121700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>32000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>32600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>122800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>30200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>29700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>32600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>34000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>95700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>34100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4673,8 +4872,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4732,8 +4934,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4791,8 +4996,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4850,8 +5058,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4909,8 +5120,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4968,53 +5182,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>37100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>40600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>42900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>91700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5027,8 +5244,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5050,53 +5270,54 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-34200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5109,8 +5330,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5168,8 +5392,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5227,53 +5454,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>289800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-37900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5286,8 +5516,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5309,8 +5542,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5330,20 +5564,20 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>-540600</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-540600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -5368,8 +5602,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5427,8 +5664,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5486,8 +5726,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5545,53 +5788,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-275200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-25700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>22200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>79800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-74300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>27800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5604,53 +5850,56 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5663,53 +5912,56 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-23200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>25800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>76300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5720,6 +5972,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>ZIMV</t>
   </si>
@@ -656,84 +656,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -746,56 +747,59 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E8" s="3">
         <v>116800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>118200</v>
       </c>
-      <c r="F8" s="3">
-        <v>457400</v>
-      </c>
       <c r="G8" s="3">
-        <v>202900</v>
+        <v>113100</v>
       </c>
       <c r="H8" s="3">
+        <v>105300</v>
+      </c>
+      <c r="I8" s="3">
         <v>118600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>120400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>463300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>214600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>234600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>235600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>261600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>753000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>274900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>637500</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -808,56 +812,59 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E9" s="3">
         <v>43500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>44300</v>
       </c>
-      <c r="F9" s="3">
-        <v>167100</v>
-      </c>
       <c r="G9" s="3">
-        <v>65200</v>
+        <v>42600</v>
       </c>
       <c r="H9" s="3">
+        <v>36900</v>
+      </c>
+      <c r="I9" s="3">
         <v>44500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>43100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>242700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>59600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>81100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>85800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>125900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>259900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>92100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>220800</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -870,56 +877,59 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>67400</v>
+      </c>
+      <c r="E10" s="3">
         <v>73300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>73900</v>
       </c>
-      <c r="F10" s="3">
-        <v>290400</v>
-      </c>
       <c r="G10" s="3">
-        <v>137700</v>
+        <v>70500</v>
       </c>
       <c r="H10" s="3">
-        <v>74100</v>
+        <v>68400</v>
       </c>
       <c r="I10" s="3">
+        <v>74200</v>
+      </c>
+      <c r="J10" s="3">
         <v>77300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>220600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>155000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>153500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>149800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>135700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>493100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>182800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>416700</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -932,8 +942,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -956,56 +969,57 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E12" s="3">
         <v>6600</v>
       </c>
-      <c r="E12" s="3">
-        <v>6800</v>
-      </c>
       <c r="F12" s="3">
-        <v>26200</v>
+        <v>6700</v>
       </c>
       <c r="G12" s="3">
-        <v>11500</v>
+        <v>6900</v>
       </c>
       <c r="H12" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I12" s="3">
         <v>6500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>46400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>43900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>36100</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1018,8 +1032,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1080,56 +1097,59 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3">
         <v>5000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3600</v>
       </c>
-      <c r="F14" s="3">
-        <v>19700</v>
-      </c>
       <c r="G14" s="3">
-        <v>4400</v>
+        <v>9800</v>
       </c>
       <c r="H14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I14" s="3">
         <v>2700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>29100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>14300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>153200</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1142,8 +1162,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1154,10 +1177,10 @@
         <v>6000</v>
       </c>
       <c r="F15" s="3">
-        <v>26500</v>
+        <v>6000</v>
       </c>
       <c r="G15" s="3">
-        <v>20600</v>
+        <v>6100</v>
       </c>
       <c r="H15" s="3">
         <v>6800</v>
@@ -1166,32 +1189,32 @@
         <v>6800</v>
       </c>
       <c r="J15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K15" s="3">
         <v>27000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>19400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>19900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>21200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>65000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>22100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>63400</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1204,8 +1227,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1225,56 +1251,57 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>123500</v>
+        <v>106100</v>
       </c>
       <c r="E17" s="3">
-        <v>121000</v>
+        <v>118500</v>
       </c>
       <c r="F17" s="3">
-        <v>488400</v>
+        <v>117300</v>
       </c>
       <c r="G17" s="3">
-        <v>219100</v>
+        <v>118500</v>
       </c>
       <c r="H17" s="3">
-        <v>123000</v>
+        <v>105900</v>
       </c>
       <c r="I17" s="3">
-        <v>126600</v>
+        <v>120300</v>
       </c>
       <c r="J17" s="3">
+        <v>124100</v>
+      </c>
+      <c r="K17" s="3">
         <v>509800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>231300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>256100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>268200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>326900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>788200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>270300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>864700</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1287,56 +1314,59 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-6700</v>
+        <v>-2900</v>
       </c>
       <c r="E18" s="3">
-        <v>-2800</v>
+        <v>-1700</v>
       </c>
       <c r="F18" s="3">
-        <v>-31000</v>
+        <v>900</v>
       </c>
       <c r="G18" s="3">
-        <v>-16200</v>
+        <v>-5400</v>
       </c>
       <c r="H18" s="3">
-        <v>-4400</v>
+        <v>-600</v>
       </c>
       <c r="I18" s="3">
-        <v>-6200</v>
+        <v>-1700</v>
       </c>
       <c r="J18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-46500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-32600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-65300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-35200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-227200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,8 +1379,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1373,56 +1406,57 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5000</v>
+        <v>-3500</v>
       </c>
       <c r="E20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>400</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L20" s="3">
+        <v>600</v>
+      </c>
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>300</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K20" s="3">
-        <v>600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1435,56 +1469,59 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="E21" s="3">
-        <v>5800</v>
+        <v>7300</v>
       </c>
       <c r="F21" s="3">
-        <v>91100</v>
+        <v>6600</v>
       </c>
       <c r="G21" s="3">
-        <v>14300</v>
+        <v>2200</v>
       </c>
       <c r="H21" s="3">
-        <v>28100</v>
+        <v>5200</v>
       </c>
       <c r="I21" s="3">
-        <v>27000</v>
+        <v>5000</v>
       </c>
       <c r="J21" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K21" s="3">
         <v>79200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-31400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>60100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>39400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-126100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1497,56 +1534,59 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E22" s="3">
         <v>5100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K22" s="3">
+        <v>10900</v>
+      </c>
+      <c r="L22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="M22" s="3">
         <v>4900</v>
       </c>
-      <c r="F22" s="3">
-        <v>20200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>9200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>5900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>5700</v>
-      </c>
-      <c r="J22" s="3">
-        <v>10900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>6200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>4900</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1559,56 +1599,59 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6800</v>
       </c>
-      <c r="E23" s="3">
-        <v>-7500</v>
-      </c>
       <c r="F23" s="3">
-        <v>-50800</v>
+        <v>-7400</v>
       </c>
       <c r="G23" s="3">
-        <v>-25500</v>
+        <v>-18700</v>
       </c>
       <c r="H23" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-9800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-54500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-26300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-33100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-65400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-35900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-226500</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,56 +1664,59 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E24" s="3">
         <v>2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4100</v>
       </c>
-      <c r="F24" s="3">
-        <v>5200</v>
-      </c>
       <c r="G24" s="3">
-        <v>-20400</v>
+        <v>3400</v>
       </c>
       <c r="H24" s="3">
+        <v>300</v>
+      </c>
+      <c r="I24" s="3">
         <v>-3800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-23100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-17600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-11000</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1683,8 +1729,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1745,56 +1794,59 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9600</v>
       </c>
-      <c r="E26" s="3">
-        <v>-11600</v>
-      </c>
       <c r="F26" s="3">
-        <v>-56000</v>
+        <v>-11500</v>
       </c>
       <c r="G26" s="3">
-        <v>-5100</v>
+        <v>-22200</v>
       </c>
       <c r="H26" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-46900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-60700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>36500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-215500</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,56 +1859,59 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-9600</v>
+        <v>-2300</v>
       </c>
       <c r="E27" s="3">
-        <v>-11600</v>
+        <v>-4000</v>
       </c>
       <c r="F27" s="3">
-        <v>-56000</v>
+        <v>-7800</v>
       </c>
       <c r="G27" s="3">
+        <v>-334900</v>
+      </c>
+      <c r="H27" s="3">
         <v>-5100</v>
       </c>
-      <c r="H27" s="3">
-        <v>-5900</v>
-      </c>
       <c r="I27" s="3">
-        <v>-16400</v>
+        <v>-23400</v>
       </c>
       <c r="J27" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-46900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-60700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>36500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-215600</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1869,8 +1924,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1931,40 +1989,43 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>800</v>
+      </c>
+      <c r="E29" s="3">
         <v>5500</v>
       </c>
-      <c r="E29" s="3">
-        <v>3800</v>
-      </c>
       <c r="F29" s="3">
-        <v>-337200</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
+        <v>3700</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-312700</v>
       </c>
       <c r="H29" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I29" s="3">
         <v>-17500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-13600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-17000</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -1993,8 +2054,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2055,8 +2119,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2117,56 +2184,59 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5000</v>
+        <v>3500</v>
       </c>
       <c r="E32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2179,56 +2249,59 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7800</v>
       </c>
-      <c r="F33" s="3">
-        <v>-393300</v>
-      </c>
       <c r="G33" s="3">
+        <v>-334900</v>
+      </c>
+      <c r="H33" s="3">
         <v>-5100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-23400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-30000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-63900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-60700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>36500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-215600</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2241,8 +2314,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2303,56 +2379,59 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7800</v>
       </c>
-      <c r="F35" s="3">
-        <v>-393300</v>
-      </c>
       <c r="G35" s="3">
+        <v>-334900</v>
+      </c>
+      <c r="H35" s="3">
         <v>-5100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-23400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-30000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-63900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-60700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>36500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-215600</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,61 +2444,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2432,8 +2514,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2456,8 +2541,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2480,50 +2566,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E41" s="3">
         <v>78600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>43500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>71500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>75400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>66200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>66400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>89600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>116000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>130100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>104300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24100</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2542,8 +2629,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2604,50 +2694,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E43" s="3">
         <v>70500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>68900</v>
       </c>
-      <c r="F43" s="3">
-        <v>65200</v>
-      </c>
       <c r="G43" s="3">
+        <v>74800</v>
+      </c>
+      <c r="H43" s="3">
         <v>153900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>168100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>175000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>177400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>172700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>188400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>180100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>164200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>170200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2666,50 +2759,53 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E44" s="3">
         <v>71800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>77200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>79600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>213700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>227500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>231100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>233900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>224200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>226500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>239300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>246800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>274700</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2728,50 +2824,53 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>52900</v>
+        <v>28100</v>
       </c>
       <c r="E45" s="3">
-        <v>265400</v>
+        <v>33800</v>
       </c>
       <c r="F45" s="3">
-        <v>266600</v>
+        <v>248700</v>
       </c>
       <c r="G45" s="3">
-        <v>54500</v>
+        <v>243600</v>
       </c>
       <c r="H45" s="3">
-        <v>45500</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
-        <v>31700</v>
+        <v>900</v>
       </c>
       <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
         <v>37000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>25400</v>
       </c>
       <c r="N45" s="3">
         <v>25400</v>
       </c>
       <c r="O45" s="3">
+        <v>25400</v>
+      </c>
+      <c r="P45" s="3">
         <v>22700</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,50 +2889,53 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>265700</v>
+      </c>
+      <c r="E46" s="3">
         <v>273900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>455100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>482900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>497600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>507400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>504200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>537900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>546200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>573900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>549100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>536800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>491700</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2852,13 +2954,16 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>60300</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -2878,8 +2983,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2914,50 +3019,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E48" s="3">
         <v>50400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>52100</v>
       </c>
-      <c r="F48" s="3">
-        <v>54200</v>
-      </c>
       <c r="G48" s="3">
+        <v>65200</v>
+      </c>
+      <c r="H48" s="3">
         <v>121400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>129700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>139300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>148400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>150300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>162900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>170500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>180200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>180700</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2976,50 +3084,53 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E49" s="3">
         <v>362800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>369800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>376500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>850600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>885800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>905200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>915000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>893900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>944600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>999000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1034000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1066700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3038,8 +3149,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3100,8 +3214,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3162,50 +3279,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E52" s="3">
         <v>42500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>294500</v>
       </c>
-      <c r="F52" s="3">
-        <v>291800</v>
-      </c>
       <c r="G52" s="3">
+        <v>280800</v>
+      </c>
+      <c r="H52" s="3">
         <v>38300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>37700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>39400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>51200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>55600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>75700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>69800</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3344,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3286,50 +3409,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>782900</v>
+      </c>
+      <c r="E54" s="3">
         <v>789800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1171600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1205300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1507900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1560500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1588100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1642100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1629400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1732600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1774300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1826700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1808900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,8 +3474,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3372,8 +3501,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3396,50 +3526,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E57" s="3">
         <v>27200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>51300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>59400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>52600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>43000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>39100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>40500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3458,34 +3589,37 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>4400</v>
       </c>
       <c r="E58" s="3">
-        <v>7000</v>
+        <v>4300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3">
-        <v>14000</v>
+        <v>10700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H58" s="3">
+        <v>10200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="J58" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>14000</v>
@@ -3494,14 +3628,14 @@
         <v>14000</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>33000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3520,50 +3654,53 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>114000</v>
+        <v>79500</v>
       </c>
       <c r="E59" s="3">
-        <v>135700</v>
+        <v>86500</v>
       </c>
       <c r="F59" s="3">
-        <v>145800</v>
+        <v>113800</v>
       </c>
       <c r="G59" s="3">
-        <v>119900</v>
+        <v>78700</v>
       </c>
       <c r="H59" s="3">
-        <v>130300</v>
+        <v>19200</v>
       </c>
       <c r="I59" s="3">
-        <v>143900</v>
+        <v>23800</v>
       </c>
       <c r="J59" s="3">
+        <v>41000</v>
+      </c>
+      <c r="K59" s="3">
         <v>173300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>162400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>189700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>166400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>139600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>128200</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3582,50 +3719,53 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E60" s="3">
         <v>141100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>169600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>173600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>171200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>189700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>196500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>217300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>217500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>246800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>219500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>184600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>201700</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,50 +3784,53 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>235100</v>
+        <v>229800</v>
       </c>
       <c r="E61" s="3">
-        <v>502100</v>
+        <v>244900</v>
       </c>
       <c r="F61" s="3">
-        <v>508800</v>
+        <v>511900</v>
       </c>
       <c r="G61" s="3">
-        <v>515500</v>
+        <v>517900</v>
       </c>
       <c r="H61" s="3">
-        <v>522300</v>
+        <v>532800</v>
       </c>
       <c r="I61" s="3">
-        <v>522000</v>
+        <v>539900</v>
       </c>
       <c r="J61" s="3">
+        <v>542600</v>
+      </c>
+      <c r="K61" s="3">
         <v>532200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>535500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>538700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>541900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>4900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3706,50 +3849,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19500</v>
+        <v>9600</v>
       </c>
       <c r="E62" s="3">
-        <v>111600</v>
+        <v>9600</v>
       </c>
       <c r="F62" s="3">
-        <v>113400</v>
+        <v>101600</v>
       </c>
       <c r="G62" s="3">
-        <v>111000</v>
+        <v>104100</v>
       </c>
       <c r="H62" s="3">
-        <v>120700</v>
+        <v>7800</v>
       </c>
       <c r="I62" s="3">
-        <v>125900</v>
+        <v>10300</v>
       </c>
       <c r="J62" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K62" s="3">
         <v>133900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>142600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>182600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>200400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>190700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>200000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3768,8 +3914,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3830,8 +3979,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3892,8 +4044,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3954,50 +4109,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>376300</v>
+      </c>
+      <c r="E66" s="3">
         <v>395700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>783300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>795900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>797700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>832700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>844500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>883500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>895600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>968000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>961800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>375300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>406600</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4016,8 +4174,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4040,8 +4201,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4102,8 +4264,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4164,8 +4329,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4226,8 +4394,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4288,44 +4459,47 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-454900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-452600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-448600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-440800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-106000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-100900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-77500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-47500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-17200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-18000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-9300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4338,8 +4512,8 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T72" s="3">
         <v>0</v>
@@ -4350,8 +4524,11 @@
       <c r="V72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4412,8 +4589,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4474,8 +4654,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4536,50 +4719,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>406600</v>
+      </c>
+      <c r="E76" s="3">
         <v>394100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>388300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>409500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>710200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>727800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>743600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>758600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>733800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>764600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>812500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1451400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1402300</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4598,8 +4784,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4660,61 +4849,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4727,56 +4919,59 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7800</v>
       </c>
-      <c r="F81" s="3">
-        <v>-393300</v>
-      </c>
       <c r="G81" s="3">
+        <v>-334900</v>
+      </c>
+      <c r="H81" s="3">
         <v>-5100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-23400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-30000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-63900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-60700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>36500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-215600</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +4984,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4813,56 +5011,57 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8500</v>
+        <v>23700</v>
       </c>
       <c r="E83" s="3">
-        <v>8400</v>
+        <v>25200</v>
       </c>
       <c r="F83" s="3">
-        <v>121700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>30500</v>
+        <v>25800</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3">
-        <v>32000</v>
+        <v>10800</v>
       </c>
       <c r="I83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="J83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K83" s="3">
+        <v>122800</v>
+      </c>
+      <c r="L83" s="3">
+        <v>30200</v>
+      </c>
+      <c r="M83" s="3">
+        <v>29700</v>
+      </c>
+      <c r="N83" s="3">
         <v>32600</v>
       </c>
-      <c r="J83" s="3">
-        <v>122800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>30200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>29700</v>
-      </c>
-      <c r="M83" s="3">
-        <v>32600</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>34000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>95700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>34100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4875,8 +5074,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4937,8 +5139,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4999,8 +5204,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5061,8 +5269,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5123,8 +5334,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5185,56 +5399,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11500</v>
       </c>
-      <c r="F89" s="3">
-        <v>37100</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>22600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>21400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>42900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>91700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5247,8 +5464,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5271,56 +5491,57 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2200</v>
       </c>
-      <c r="F91" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
-        <v>-3800</v>
-      </c>
       <c r="J91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-5400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-34200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3700</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5333,8 +5554,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5395,8 +5619,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5457,56 +5684,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>289800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4100</v>
       </c>
-      <c r="F94" s="3">
-        <v>-15200</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
         <v>-5300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-37900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-29400</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5519,8 +5749,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5543,44 +5776,45 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K96" s="3">
         <v>-540600</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-540600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -5605,8 +5839,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5667,8 +5904,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5729,8 +5969,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5791,56 +6034,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-275200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1400</v>
       </c>
-      <c r="F100" s="3">
-        <v>-25700</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>-7000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>22200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>79800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-74300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>27800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5853,56 +6099,59 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-3500</v>
+        <v>-1000</v>
       </c>
       <c r="E101" s="3">
-        <v>-2100</v>
+        <v>-400</v>
       </c>
       <c r="F101" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-1000</v>
+        <v>800</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
-        <v>-400</v>
+        <v>-4500</v>
       </c>
       <c r="I101" s="3">
-        <v>800</v>
+        <v>-5200</v>
       </c>
       <c r="J101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-5500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-900</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5915,56 +6164,59 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E102" s="3">
         <v>14100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19200</v>
       </c>
-      <c r="F102" s="3">
-        <v>-1800</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>9200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-23200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>25800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>76300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5975,6 +6227,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
   <si>
     <t>ZIMV</t>
   </si>
@@ -656,88 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -750,59 +750,62 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E8" s="3">
         <v>103200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>116800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>118200</v>
       </c>
-      <c r="G8" s="3">
-        <v>113100</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>105300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>118600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>120400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>463300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>214600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>234600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>235600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>261600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>753000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>274900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>637500</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -815,59 +818,62 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E9" s="3">
         <v>35800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>43500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>44300</v>
       </c>
-      <c r="G9" s="3">
-        <v>42600</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3">
         <v>36900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>44500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>43100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>242700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>59600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>81100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>85800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>125900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>259900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>92100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>220800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -880,59 +886,62 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E10" s="3">
         <v>67400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>73300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>73900</v>
       </c>
-      <c r="G10" s="3">
-        <v>70500</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
         <v>68400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>74200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>77300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>220600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>155000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>153500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>149800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>135700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>493100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>182800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>416700</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -945,8 +954,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -970,59 +982,60 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E12" s="3">
         <v>6900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6700</v>
       </c>
-      <c r="G12" s="3">
-        <v>6900</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
         <v>5700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>46400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>43900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>36100</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1035,8 +1048,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1100,59 +1116,62 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3600</v>
       </c>
-      <c r="G14" s="3">
-        <v>9800</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>3300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>29100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>153200</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1165,8 +1184,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1180,10 +1202,10 @@
         <v>6000</v>
       </c>
       <c r="G15" s="3">
-        <v>6100</v>
+        <v>6000</v>
       </c>
       <c r="H15" s="3">
-        <v>6800</v>
+        <v>8600</v>
       </c>
       <c r="I15" s="3">
         <v>6800</v>
@@ -1192,32 +1214,32 @@
         <v>6800</v>
       </c>
       <c r="K15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="L15" s="3">
         <v>27000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>19400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>19900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>20900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>21200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>65000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>22100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>63400</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,8 +1252,11 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1252,59 +1277,60 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>109900</v>
+      </c>
+      <c r="E17" s="3">
         <v>106100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>118500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>117300</v>
       </c>
-      <c r="G17" s="3">
-        <v>118500</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3">
         <v>105900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>120300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>124100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>509800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>231300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>256100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>268200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>326900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>788200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>270300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>864700</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,59 +1343,62 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-46500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-65300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-227200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1382,8 +1411,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1407,59 +1439,60 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1472,59 +1505,62 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E21" s="3">
         <v>6600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6600</v>
       </c>
-      <c r="G21" s="3">
-        <v>2200</v>
-      </c>
       <c r="H21" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I21" s="3">
         <v>5200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>79200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-31400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>60100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>39400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-126100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1537,59 +1573,62 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E22" s="3">
         <v>4800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4400</v>
       </c>
-      <c r="G22" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>5600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1602,59 +1641,62 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7400</v>
       </c>
-      <c r="G23" s="3">
-        <v>-18700</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3">
         <v>-9900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-54500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-22300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-33100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-65400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-226500</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1667,59 +1709,62 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4100</v>
       </c>
-      <c r="G24" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-23100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-17600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-31300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-11000</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1732,8 +1777,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1797,59 +1845,62 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-22200</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3">
         <v>-10200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-46900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-60700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>36500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-215500</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1862,59 +1913,62 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7800</v>
       </c>
-      <c r="G27" s="3">
-        <v>-334900</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3">
         <v>-5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-30000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-46900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-60700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>36500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-215600</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1927,8 +1981,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1992,43 +2049,46 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E29" s="3">
         <v>800</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>5500</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>3700</v>
       </c>
-      <c r="G29" s="3">
-        <v>-312700</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>5100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-17500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-13600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-17000</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2057,8 +2117,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2122,8 +2185,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2187,59 +2253,62 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E32" s="3">
         <v>3500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2252,59 +2321,62 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7800</v>
       </c>
-      <c r="G33" s="3">
-        <v>-334900</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3">
         <v>-5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-30000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-63900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-60700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>36500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-215600</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2317,8 +2389,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2382,59 +2457,62 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7800</v>
       </c>
-      <c r="G35" s="3">
-        <v>-334900</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3">
         <v>-5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-30000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-63900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-60700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>36500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-215600</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2447,64 +2525,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2517,8 +2598,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2542,8 +2626,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2567,53 +2652,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E41" s="3">
         <v>66800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>78600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>71500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>75400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>66200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>89600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>116000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>130100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>104300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>100400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24100</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2632,8 +2718,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2697,53 +2786,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E43" s="3">
         <v>69600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>70500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>68900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>74800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>153900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>168100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>175000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>177400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>172700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>188400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>180100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>164200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>170200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2762,53 +2854,56 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E44" s="3">
         <v>77100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>71800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>77200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>79600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>213700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>227500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>231100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>233900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>224200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>226500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>239300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>246800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>274700</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2827,53 +2922,56 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E45" s="3">
         <v>28100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>33800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>248700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>243600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>37000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>25400</v>
       </c>
       <c r="O45" s="3">
         <v>25400</v>
       </c>
       <c r="P45" s="3">
+        <v>25400</v>
+      </c>
+      <c r="Q45" s="3">
         <v>22700</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,53 +2990,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="E46" s="3">
         <v>265700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>273900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>455100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>482900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>497600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>507400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>504200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>537900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>546200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>573900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>549100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>536800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>491700</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,8 +3058,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2986,8 +3090,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3022,53 +3126,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E48" s="3">
         <v>49600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>50400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>52100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>65200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>121400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>129700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>139300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>148400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>150300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>162900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>170500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>180200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>180700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3087,53 +3194,56 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>350300</v>
+      </c>
+      <c r="E49" s="3">
         <v>361000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>362800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>369800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>376500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>850600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>885800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>905200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>915000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>893900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>944600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>999000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1034000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1066700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3152,8 +3262,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3217,8 +3330,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3282,53 +3398,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E52" s="3">
         <v>43600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>42500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>294500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>280800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>38300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>37700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>39400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>40800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>51200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>55600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>75700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>69800</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,8 +3466,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3412,53 +3534,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>753700</v>
+      </c>
+      <c r="E54" s="3">
         <v>782900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>789800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1171600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1205300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1507900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1560500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1588100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1642100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1629400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1732600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1774300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1826700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1808900</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3477,8 +3602,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3502,8 +3630,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3527,53 +3656,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E57" s="3">
         <v>27400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>51300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>59400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>52600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>44000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>39100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>45000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>40500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3592,37 +3722,40 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E58" s="3">
         <v>4400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9600</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>14000</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>14000</v>
@@ -3631,14 +3764,14 @@
         <v>14000</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>33000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3657,53 +3790,56 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E59" s="3">
         <v>79500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>86500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>113800</v>
       </c>
-      <c r="G59" s="3">
-        <v>78700</v>
-      </c>
       <c r="H59" s="3">
+        <v>118600</v>
+      </c>
+      <c r="I59" s="3">
         <v>19200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>41000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>173300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>162400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>189700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>166400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>139600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>128200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,53 +3858,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E60" s="3">
         <v>136600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>141100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>169600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>173600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>171200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>189700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>196500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>217300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>217500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>246800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>219500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>184600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>201700</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3787,53 +3926,56 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>228700</v>
+      </c>
+      <c r="E61" s="3">
         <v>229800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>244900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>511900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>517900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>532800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>539900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>542600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>532200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>535500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>538700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>541900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>4900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3852,53 +3994,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9600</v>
+        <v>9400</v>
       </c>
       <c r="E62" s="3">
         <v>9600</v>
       </c>
       <c r="F62" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G62" s="3">
         <v>101600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>104100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>133900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>142600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>182600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>200400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>190700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>200000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3917,8 +4062,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3982,8 +4130,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4047,8 +4198,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4112,53 +4266,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>372000</v>
+      </c>
+      <c r="E66" s="3">
         <v>376300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>395700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>783300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>795900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>797700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>832700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>844500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>883500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>895600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>968000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>961800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>375300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>406600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4334,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4202,8 +4362,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4267,8 +4428,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4332,8 +4496,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4397,8 +4564,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4462,47 +4632,50 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-466600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-454900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-452600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-448600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-440800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-106000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-100900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-77500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-47500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-17200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-18000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-9300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4688,8 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U72" s="3">
         <v>0</v>
@@ -4527,8 +4700,11 @@
       <c r="W72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4592,8 +4768,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4657,8 +4836,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4722,53 +4904,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>381700</v>
+      </c>
+      <c r="E76" s="3">
         <v>406600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>394100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>388300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>409500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>710200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>727800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>743600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>758600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>733800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>764600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>812500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1451400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1402300</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4787,8 +4972,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4852,64 +5040,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4922,59 +5113,62 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7800</v>
       </c>
-      <c r="G81" s="3">
-        <v>-334900</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3">
         <v>-5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-30000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-63900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-60700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>36500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-215600</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4987,8 +5181,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5012,59 +5209,60 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>23700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>25800</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3">
         <v>10800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>122800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>34000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>95700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>34100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>100200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5077,8 +5275,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5142,8 +5343,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5207,8 +5411,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5272,8 +5479,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5337,8 +5547,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5402,59 +5615,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11500</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3">
         <v>22600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>40600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>42900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>91700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5700</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5683,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5492,59 +5711,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3700</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5557,8 +5777,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5622,8 +5845,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5687,59 +5913,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>289800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4100</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>-5300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-20100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-29400</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5752,8 +5981,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5777,8 +6009,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5803,21 +6036,21 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3">
         <v>-540600</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-540600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -5842,8 +6075,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5907,8 +6143,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5972,8 +6211,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6037,59 +6279,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-275200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1400</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>-7000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-10900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>22200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>79800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-74300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>27800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6102,59 +6347,62 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3">
         <v>-4500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6167,59 +6415,62 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19200</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>9200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-23200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>76300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6230,6 +6481,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>ZIMV</t>
   </si>
@@ -656,91 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -753,62 +754,65 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E8" s="3">
         <v>111500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>103200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>116800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>118200</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>105300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>118600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>120400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>463300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>214600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>234600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>235600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>261600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>753000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>274900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>637500</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -821,62 +825,65 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E9" s="3">
         <v>38700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>35800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>43500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>44300</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
         <v>36900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>44500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>43100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>242700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>59600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>81100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>85800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>125900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>259900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>92100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>220800</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -889,62 +896,65 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E10" s="3">
         <v>72800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>67400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>73300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>73900</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
         <v>68400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>74200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>77300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>220600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>155000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>153500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>149800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>135700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>493100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>182800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>416700</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -957,8 +967,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -983,62 +996,63 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E12" s="3">
         <v>6600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6700</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>5700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>46400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>14500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>43900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>36100</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1051,8 +1065,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1119,62 +1136,65 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>800</v>
+      </c>
+      <c r="E14" s="3">
         <v>8000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3600</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>3300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>29100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>14300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>153200</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1187,8 +1207,11 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1205,10 +1228,10 @@
         <v>6000</v>
       </c>
       <c r="H15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I15" s="3">
         <v>8600</v>
-      </c>
-      <c r="I15" s="3">
-        <v>6800</v>
       </c>
       <c r="J15" s="3">
         <v>6800</v>
@@ -1217,32 +1240,32 @@
         <v>6800</v>
       </c>
       <c r="L15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M15" s="3">
         <v>27000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>19400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>20900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>21200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>65000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>22100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>63400</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1255,8 +1278,11 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1278,62 +1304,63 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>108300</v>
+      </c>
+      <c r="E17" s="3">
         <v>109900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>106100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>118500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>117300</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
         <v>105900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>120300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>124100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>509800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>231300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>256100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>268200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>326900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>788200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>270300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>864700</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1346,62 +1373,65 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E18" s="3">
         <v>1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>900</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-46500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-32600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-35200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-227200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1414,8 +1444,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1440,62 +1473,63 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1508,62 +1542,65 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E21" s="3">
         <v>10400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>79200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>60100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>39400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-126100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,8 +1613,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1585,53 +1625,53 @@
         <v>4100</v>
       </c>
       <c r="E22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F22" s="3">
         <v>4800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5100</v>
       </c>
-      <c r="G22" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="H22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>5600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,62 +1684,65 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7400</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
         <v>-9900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-54500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-22300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-26300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-33100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-65400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-35900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-226500</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,62 +1755,65 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E24" s="3">
         <v>4100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-23100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-17600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-7400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-31300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-11000</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1780,8 +1826,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1848,62 +1897,65 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11500</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3">
         <v>-10200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-46900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-60700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-34600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>36500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-215500</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1916,62 +1968,65 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7800</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3">
         <v>-5100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-30000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-46900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-60700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-34600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>36500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-215600</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1984,8 +2039,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2052,46 +2110,49 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E29" s="3">
         <v>-2100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>800</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>5500</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>3700</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>5100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-17500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-13600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-17000</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2120,8 +2181,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2188,8 +2252,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2256,62 +2323,65 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>2700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2324,62 +2394,65 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7800</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3">
         <v>-5100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-30000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-63900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-60700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-34600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>36500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-215600</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,8 +2465,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2460,62 +2536,65 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7800</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3">
         <v>-5100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-30000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-63900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-60700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-34600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>36500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-215600</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,67 +2607,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2601,8 +2683,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2627,8 +2712,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2653,56 +2739,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E41" s="3">
         <v>75000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>66800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>43500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>75400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>89600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>116000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>130100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>104300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>100400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24100</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2721,8 +2808,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2789,56 +2879,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E43" s="3">
         <v>71900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>69600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>70500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>68900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>74800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>153900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>168100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>175000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>177400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>172700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>188400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>180100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>164200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>170200</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,56 +2950,59 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>77700</v>
+      </c>
+      <c r="E44" s="3">
         <v>75000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>77100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>71800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>77200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>79600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>213700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>227500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>231100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>233900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>224200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>226500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>239300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>246800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>274700</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,56 +3021,59 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E45" s="3">
         <v>19500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>248700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>243600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>37000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28900</v>
-      </c>
-      <c r="O45" s="3">
-        <v>25400</v>
       </c>
       <c r="P45" s="3">
         <v>25400</v>
       </c>
       <c r="Q45" s="3">
+        <v>25400</v>
+      </c>
+      <c r="R45" s="3">
         <v>22700</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,56 +3092,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>250700</v>
+      </c>
+      <c r="E46" s="3">
         <v>257300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>265700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>273900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>455100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>482900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>497600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>507400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>504200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>537900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>546200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>573900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>549100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>536800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>491700</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,8 +3163,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3093,8 +3198,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3129,56 +3234,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E48" s="3">
         <v>57900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>49600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>50400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>52100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>65200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>121400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>129700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>139300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>148400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>150300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>162900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>170500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>180200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>180700</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3197,56 +3305,59 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>350100</v>
+      </c>
+      <c r="E49" s="3">
         <v>350300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>361000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>362800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>369800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>376500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>850600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>885800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>905200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>915000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>893900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>944600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>999000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1034000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1066700</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,8 +3376,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3333,8 +3447,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3401,56 +3518,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E52" s="3">
         <v>23500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>43600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>42500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>294500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>280800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>38300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>37700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>39400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>40800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>51200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>55600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>75700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>69800</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3589,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3537,56 +3660,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>745800</v>
+      </c>
+      <c r="E54" s="3">
         <v>753700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>782900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>789800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1171600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1205300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1507900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1560500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1588100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1642100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1629400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1732600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1774300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1826700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1808900</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3605,8 +3731,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3631,8 +3760,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3657,56 +3787,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E57" s="3">
         <v>33000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>51300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>59400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>52600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>44000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>43000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>39100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>40500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,8 +3856,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3734,31 +3868,31 @@
         <v>3900</v>
       </c>
       <c r="E58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F58" s="3">
         <v>4400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9600</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
-        <v>14000</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>14000</v>
@@ -3767,14 +3901,14 @@
         <v>14000</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>33000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3793,56 +3927,59 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E59" s="3">
         <v>75500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>79500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>86500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>113800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>118600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>41000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>173300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>162400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>189700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>166400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>139600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>128200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,56 +3998,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E60" s="3">
         <v>133900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>136600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>141100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>169600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>173600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>171200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>189700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>196500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>217300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>217500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>246800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>219500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>184600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>201700</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3929,56 +4069,59 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>228900</v>
+      </c>
+      <c r="E61" s="3">
         <v>228700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>229800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>244900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>511900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>517900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>532800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>539900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>542600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>532200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>535500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>538700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>541900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>4900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3997,56 +4140,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E62" s="3">
         <v>9400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>9600</v>
       </c>
       <c r="F62" s="3">
         <v>9600</v>
       </c>
       <c r="G62" s="3">
+        <v>9600</v>
+      </c>
+      <c r="H62" s="3">
         <v>101600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>104100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>133900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>142600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>182600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>200400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>190700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>200000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4065,8 +4211,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4133,8 +4282,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4201,8 +4353,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4269,56 +4424,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>350700</v>
+      </c>
+      <c r="E66" s="3">
         <v>372000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>376300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>395700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>783300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>795900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>797700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>832700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>844500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>883500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>895600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>968000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>961800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>375300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>406600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4337,8 +4495,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4363,8 +4524,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4431,8 +4593,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4499,8 +4664,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4567,8 +4735,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4635,50 +4806,53 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-468100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-466600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-454900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-452600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-448600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-440800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-106000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-100900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-77500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-47500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-17200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-18000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-9300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4691,8 +4865,8 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
@@ -4703,8 +4877,11 @@
       <c r="X72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4771,8 +4948,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4839,8 +5019,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4907,56 +5090,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>395100</v>
+      </c>
+      <c r="E76" s="3">
         <v>381700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>406600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>394100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>388300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>409500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>710200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>727800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>743600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>758600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>733800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>764600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>812500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1451400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1402300</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4975,8 +5161,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5043,67 +5232,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5116,62 +5308,65 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7800</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3">
         <v>-5100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-30000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-63900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-60700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-34600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>36500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-215600</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5184,8 +5379,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5210,62 +5408,63 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>23700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>25200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25800</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>10800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>122800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>29700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>32600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>34000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>95700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>34100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>100200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5278,8 +5477,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5346,8 +5548,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5414,8 +5619,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5482,8 +5690,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5550,8 +5761,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5618,62 +5832,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E89" s="3">
         <v>21500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11500</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>22600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>24600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>40600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>42900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>91700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5700</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5686,8 +5903,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5712,62 +5932,63 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-34200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5780,8 +6001,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5848,8 +6072,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5916,62 +6143,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>289800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4100</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-5300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-28700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-37900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-29400</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5984,8 +6214,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6010,8 +6243,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6039,21 +6273,21 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3">
         <v>-540600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-540600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -6078,8 +6312,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6146,8 +6383,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6214,8 +6454,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6282,62 +6525,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-275200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1400</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>-7000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>22200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>79800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-74300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>27800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6350,62 +6596,65 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>-4500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6418,62 +6667,65 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E102" s="3">
         <v>8500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-19200</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>9200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-23200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>25800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>76300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6484,6 +6736,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIMV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>ZIMV</t>
   </si>
@@ -656,95 +656,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -757,65 +758,68 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>116700</v>
+      </c>
+      <c r="E8" s="3">
         <v>112000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>111500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>103200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>116800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>118200</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>105300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>118600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>120400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>463300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>214600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>234600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>235600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>261600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>753000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>274900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>637500</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -828,65 +832,68 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E9" s="3">
         <v>37900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>38700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>35800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>43500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>44300</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>36900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>44500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>43100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>242700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>59600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>81100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>85800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>125900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>259900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>92100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>220800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -899,65 +906,68 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E10" s="3">
         <v>74000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>72800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>67400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>73300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>73900</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>68400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>77300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>220600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>155000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>153500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>149800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>135700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>493100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>182800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>416700</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -970,8 +980,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -997,65 +1010,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E12" s="3">
         <v>5400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6700</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>5700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>46400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>43900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>36100</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1068,8 +1082,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1139,65 +1156,68 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>3300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>29100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>14300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>153200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1210,13 +1230,16 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="E15" s="3">
         <v>6000</v>
@@ -1231,10 +1254,10 @@
         <v>6000</v>
       </c>
       <c r="I15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J15" s="3">
         <v>8600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>6800</v>
       </c>
       <c r="K15" s="3">
         <v>6800</v>
@@ -1243,32 +1266,32 @@
         <v>6800</v>
       </c>
       <c r="M15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="N15" s="3">
         <v>27000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>19900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>21200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>65000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>22100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>63400</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1281,8 +1304,11 @@
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1305,65 +1331,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>112800</v>
+      </c>
+      <c r="E17" s="3">
         <v>108300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>109900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>106100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>118500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>117300</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
         <v>105900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>120300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>124100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>509800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>231300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>256100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>268200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>326900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>788200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>270300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>864700</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1376,65 +1403,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E18" s="3">
         <v>3700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>900</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-46500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-65300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-35200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-227200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1447,8 +1477,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1474,65 +1507,66 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1545,65 +1579,68 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E21" s="3">
         <v>9300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>79200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-31400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>60100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>39400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-126100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1616,65 +1653,68 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="E22" s="3">
         <v>4100</v>
       </c>
       <c r="F22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G22" s="3">
         <v>4800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4900</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>5600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1687,65 +1727,68 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>300</v>
+      </c>
+      <c r="E23" s="3">
         <v>400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7400</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
         <v>-9900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-54500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-22300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-65400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-35900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-226500</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1758,65 +1801,68 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>3100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-23100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-17600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-31300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1829,8 +1875,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1900,65 +1949,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11500</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
         <v>-10200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-46900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-60700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-34600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>36500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-215500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1971,65 +2023,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7800</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-46900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-60700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-34600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>36500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-215600</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2042,8 +2097,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2113,49 +2171,52 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E29" s="3">
         <v>1200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-2100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>800</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>5500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>3700</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>5100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-17500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-13600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-17000</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2184,8 +2245,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2255,8 +2319,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2326,65 +2393,68 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2397,65 +2467,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7800</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-63900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-60700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-34600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>36500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-215600</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2468,8 +2541,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2539,65 +2615,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7800</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-63900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-60700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-34600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>36500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-215600</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2610,70 +2689,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2686,8 +2768,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2713,8 +2798,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2740,59 +2826,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E41" s="3">
         <v>66800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>75000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>66800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>78600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>71500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>75400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>89600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>116000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>130100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>104300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>100400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24100</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2811,8 +2898,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2882,59 +2972,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E43" s="3">
         <v>76700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>71900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>69600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>70500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>68900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>74800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>153900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>168100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>175000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>177400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>172700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>188400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>180100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>164200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>170200</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2953,59 +3046,62 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>84400</v>
+      </c>
+      <c r="E44" s="3">
         <v>77700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>75000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>77100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>71800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>77200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>79600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>213700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>227500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>231100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>233900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>224200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>226500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>239300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>246800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>274700</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,59 +3120,62 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E45" s="3">
         <v>13600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>19500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>248700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>243600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>25400</v>
       </c>
       <c r="Q45" s="3">
         <v>25400</v>
       </c>
       <c r="R45" s="3">
+        <v>25400</v>
+      </c>
+      <c r="S45" s="3">
         <v>22700</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,59 +3194,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>260200</v>
+      </c>
+      <c r="E46" s="3">
         <v>250700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>257300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>265700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>273900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>455100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>482900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>497600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>507400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>504200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>537900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>546200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>573900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>549100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>536800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>491700</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,8 +3268,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3201,8 +3306,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3237,59 +3342,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E48" s="3">
         <v>46900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>57900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>49600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>50400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>52100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>65200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>121400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>129700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>139300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>148400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>150300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>162900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>170500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>180200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>180700</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3308,59 +3416,62 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>352700</v>
+      </c>
+      <c r="E49" s="3">
         <v>350100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>350300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>361000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>362800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>369800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>376500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>850600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>885800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>905200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>915000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>893900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>944600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>999000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1034000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1066700</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3490,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3450,8 +3564,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3521,59 +3638,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E52" s="3">
         <v>32100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>43600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>294500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>280800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>37700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>39400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>40800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>38900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>51200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>55600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>75700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>69800</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3592,8 +3712,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3663,59 +3786,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>758200</v>
+      </c>
+      <c r="E54" s="3">
         <v>745800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>753700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>782900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>789800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1171600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1205300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1507900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1560500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1588100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1642100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1629400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1732600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1774300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1826700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1808900</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3734,8 +3860,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3761,8 +3890,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3788,59 +3918,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E57" s="3">
         <v>31500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>27800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>51300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>52600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>44000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>43000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>39100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>45000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>40500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3859,43 +3990,46 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3900</v>
+        <v>3700</v>
       </c>
       <c r="E58" s="3">
         <v>3900</v>
       </c>
       <c r="F58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G58" s="3">
         <v>4400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9600</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
-        <v>14000</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>14000</v>
@@ -3904,14 +4038,14 @@
         <v>14000</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>33000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3930,59 +4064,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E59" s="3">
         <v>57400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>75500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>79500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>86500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>113800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>118600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>173300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>162400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>189700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>166400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>139600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>128200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,59 +4138,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>109600</v>
+      </c>
+      <c r="E60" s="3">
         <v>117100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>133900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>136600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>141100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>169600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>173600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>171200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>189700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>196500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>217300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>217500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>246800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>219500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>184600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>201700</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4072,59 +4212,62 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>230900</v>
+      </c>
+      <c r="E61" s="3">
         <v>228900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>228700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>229800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>244900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>511900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>517900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>532800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>539900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>542600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>532200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>535500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>538700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>541900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>4900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4143,59 +4286,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E62" s="3">
         <v>4600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>9600</v>
       </c>
       <c r="G62" s="3">
         <v>9600</v>
       </c>
       <c r="H62" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I62" s="3">
         <v>101600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>104100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>133900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>142600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>182600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>200400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>190700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>200000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4214,8 +4360,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4285,8 +4434,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4356,8 +4508,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4427,59 +4582,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>345400</v>
+      </c>
+      <c r="E66" s="3">
         <v>350700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>372000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>376300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>395700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>783300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>795900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>797700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>832700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>844500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>883500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>895600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>968000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>961800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>375300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>406600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4498,8 +4656,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4525,8 +4686,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4596,8 +4758,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4667,8 +4832,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4738,8 +4906,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4809,53 +4980,56 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-472100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-468100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-466600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-454900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-452600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-448600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-440800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-106000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-100900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-77500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-47500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-18000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4868,8 +5042,8 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -4880,8 +5054,11 @@
       <c r="Y72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4951,8 +5128,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5022,8 +5202,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5093,59 +5276,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>412800</v>
+      </c>
+      <c r="E76" s="3">
         <v>395100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>381700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>406600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>394100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>388300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>409500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>710200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>727800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>743600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>758600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>733800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>764600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>812500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1451400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1402300</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5164,8 +5350,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5235,70 +5424,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5311,65 +5503,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7800</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-63900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-60700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-34600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>36500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-215600</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5382,8 +5577,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5409,65 +5607,66 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E83" s="3">
         <v>2400</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3">
         <v>23700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25800</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>10800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>122800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>29700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>32600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>34000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>95700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>34100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>100200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5480,8 +5679,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5551,8 +5753,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5622,8 +5827,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5693,8 +5901,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5764,8 +5975,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5835,65 +6049,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11500</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>22600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>24600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>42900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>91700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5700</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5906,8 +6123,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5933,65 +6153,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-22400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-34200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3700</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6004,8 +6225,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6075,8 +6299,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6146,65 +6373,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>289800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4100</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-5300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-37900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-20100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-29400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6217,8 +6447,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6244,8 +6477,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6276,21 +6510,21 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3">
         <v>-540600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-540600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -6315,8 +6549,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6386,8 +6623,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6457,8 +6697,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6528,65 +6771,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-275200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1400</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>-7000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>22200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>79800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-74300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>27800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6599,65 +6845,68 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2100</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-4500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6670,65 +6919,68 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19200</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>9200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-23200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>76300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6739,6 +6991,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
